--- a/Documentation/Week 2/Booked Hours/Booked_Hours_Dylan.xlsx
+++ b/Documentation/Week 2/Booked Hours/Booked_Hours_Dylan.xlsx
@@ -5,12 +5,12 @@
   <workbookPr date1904="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniwa-my.sharepoint.com/personal/24314441_student_uwa_edu_au/Documents/UWA/Year 3/Sem 2/CITS3200_Project/Documentation/Week 2/Booked Hours/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniwa-my.sharepoint.com/personal/24432207_student_uwa_edu_au/Documents/UWA - Student/2026_Sem2/CITS3200 - Professional Computing/Project/Repo/CITS3200_Project/Documentation/Week 2/Booked Hours/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:40009_{31A31D98-CA30-574B-8C94-F50C456CB544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D4B874F9-0B1B-4F80-A05F-5B57E19FE341}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="13_ncr:40009_{31A31D98-CA30-574B-8C94-F50C456CB544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D801A110-74F6-4B48-9EF8-17038917DE2B}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BookedHours" sheetId="1" r:id="rId1"/>
@@ -63,8 +63,14 @@
 Hours</t>
   </si>
   <si>
+    <t>Team meeting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meeting with client </t>
+  </si>
+  <si>
     <r>
-      <t>CITS3200 Project Billed Hours Record for &lt;YOUR NAME GOES HERE&gt;</t>
+      <t>CITS3200 Project Billed Hours Record for &lt;Dylan Hu&gt;</t>
     </r>
     <r>
       <rPr>
@@ -75,12 +81,6 @@
       <t xml:space="preserve">
 Each time you do some work on the project, note the week number, start and end date and hour, plus a brief description of the activity. At the end of each week send a copy of the sheet as it currently stands to your group's manager for recording on the group TimeSheet. Date in the form DD/MM/YY and time as XX:YY (24hr clock)</t>
     </r>
-  </si>
-  <si>
-    <t>Team meeting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Meeting with client </t>
   </si>
 </sst>
 </file>
@@ -772,7 +772,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="70.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -839,13 +839,13 @@
         <v>0.5</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G4" s="6">
         <v>0.99999999994179234</v>
       </c>
       <c r="H4" s="1">
-        <v>2.25</v>
+        <v>1</v>
       </c>
       <c r="I4" s="1">
         <f>((D4+E4)-(B4+C4))*24</f>
@@ -866,22 +866,22 @@
         <v>44771</v>
       </c>
       <c r="E5" s="5">
-        <v>0.59375</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G5" s="6">
         <f t="shared" ref="G5" si="0">IF(I5&gt;0,I5,IF(I5=0, " ", "ERROR"))</f>
-        <v>0.75</v>
+        <v>0.99999999994179234</v>
       </c>
       <c r="H5" s="1">
         <f>IF(AND(G5&lt;&gt;" ",G5&lt;&gt;"ERROR",H4&lt;&gt;" ", H4&lt;&gt;"ERROR"),G5+H4," ")</f>
-        <v>3</v>
+        <v>1.9999999999417923</v>
       </c>
       <c r="I5" s="1">
         <f t="shared" ref="I5:I68" si="1">((D5+E5)-(B5+C5))*24</f>
-        <v>0.75</v>
+        <v>0.99999999994179234</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
@@ -890,7 +890,7 @@
       <c r="D6" s="4"/>
       <c r="E6" s="5"/>
       <c r="G6" s="6" t="str">
-        <f t="shared" ref="G5:G30" si="2">IF(I6&gt;0,I6,IF(I6=0, " ", "ERROR"))</f>
+        <f t="shared" ref="G6:G30" si="2">IF(I6&gt;0,I6,IF(I6=0, " ", "ERROR"))</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="H6" s="1" t="str">

--- a/Documentation/Week 2/Booked Hours/Booked_Hours_Dylan.xlsx
+++ b/Documentation/Week 2/Booked Hours/Booked_Hours_Dylan.xlsx
@@ -5,12 +5,12 @@
   <workbookPr date1904="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniwa-my.sharepoint.com/personal/24432207_student_uwa_edu_au/Documents/UWA - Student/2026_Sem2/CITS3200 - Professional Computing/Project/Repo/CITS3200_Project/Documentation/Week 2/Booked Hours/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniwa-my.sharepoint.com/personal/24314441_student_uwa_edu_au/Documents/UWA/Year 3/Sem 2/CITS3200_Project/Documentation/Week 2/Booked Hours/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="13_ncr:40009_{31A31D98-CA30-574B-8C94-F50C456CB544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D801A110-74F6-4B48-9EF8-17038917DE2B}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:40009_{31A31D98-CA30-574B-8C94-F50C456CB544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D4B874F9-0B1B-4F80-A05F-5B57E19FE341}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BookedHours" sheetId="1" r:id="rId1"/>
@@ -63,14 +63,8 @@
 Hours</t>
   </si>
   <si>
-    <t>Team meeting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Meeting with client </t>
-  </si>
-  <si>
     <r>
-      <t>CITS3200 Project Billed Hours Record for &lt;Dylan Hu&gt;</t>
+      <t>CITS3200 Project Billed Hours Record for &lt;YOUR NAME GOES HERE&gt;</t>
     </r>
     <r>
       <rPr>
@@ -81,6 +75,12 @@
       <t xml:space="preserve">
 Each time you do some work on the project, note the week number, start and end date and hour, plus a brief description of the activity. At the end of each week send a copy of the sheet as it currently stands to your group's manager for recording on the group TimeSheet. Date in the form DD/MM/YY and time as XX:YY (24hr clock)</t>
     </r>
+  </si>
+  <si>
+    <t>Team meeting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meeting with client </t>
   </si>
 </sst>
 </file>
@@ -772,7 +772,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="70.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -839,13 +839,13 @@
         <v>0.5</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G4" s="6">
         <v>0.99999999994179234</v>
       </c>
       <c r="H4" s="1">
-        <v>1</v>
+        <v>2.25</v>
       </c>
       <c r="I4" s="1">
         <f>((D4+E4)-(B4+C4))*24</f>
@@ -866,22 +866,22 @@
         <v>44771</v>
       </c>
       <c r="E5" s="5">
-        <v>0.60416666666666663</v>
+        <v>0.59375</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G5" s="6">
         <f t="shared" ref="G5" si="0">IF(I5&gt;0,I5,IF(I5=0, " ", "ERROR"))</f>
-        <v>0.99999999994179234</v>
+        <v>0.75</v>
       </c>
       <c r="H5" s="1">
         <f>IF(AND(G5&lt;&gt;" ",G5&lt;&gt;"ERROR",H4&lt;&gt;" ", H4&lt;&gt;"ERROR"),G5+H4," ")</f>
-        <v>1.9999999999417923</v>
+        <v>3</v>
       </c>
       <c r="I5" s="1">
         <f t="shared" ref="I5:I68" si="1">((D5+E5)-(B5+C5))*24</f>
-        <v>0.99999999994179234</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
@@ -890,7 +890,7 @@
       <c r="D6" s="4"/>
       <c r="E6" s="5"/>
       <c r="G6" s="6" t="str">
-        <f t="shared" ref="G6:G30" si="2">IF(I6&gt;0,I6,IF(I6=0, " ", "ERROR"))</f>
+        <f t="shared" ref="G5:G30" si="2">IF(I6&gt;0,I6,IF(I6=0, " ", "ERROR"))</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="H6" s="1" t="str">
